--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -151,6 +151,15 @@
   </si>
   <si>
     <t>The player of the role is the primary caretaker of the scoping person.</t>
+  </si>
+  <si>
+    <t>PROCON</t>
+  </si>
+  <si>
+    <t>Professional contact</t>
+  </si>
+  <si>
+    <t>A professional acting as a contact of the scoping person.</t>
   </si>
 </sst>
 </file>
@@ -460,7 +469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -505,6 +514,20 @@
         <v>45</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
+++ b/CodeSystem-dk-relatedperson-relationshipcodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
